--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00126_19130805.3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00126_19130805.3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,19 +581,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>L47: possible duplicated/overlap line with previous line (similarity 68%) :: mirror 16Ã—18, 4 large drawers</t>
-        </is>
-      </c>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
         <is>
@@ -802,7 +798,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -931,12 +927,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00126_19130805.3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00126_19130805.3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="56" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” AT-</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]rentes</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]rentes</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 3</t>
@@ -638,7 +642,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L715: line starts with punctuation glued to text :: * SILK and CREPE KIMONAS. SEPARATE SKIRTS-In White</t>
+          <t>L259: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Gleaner will be published on •</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>564</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -684,12 +688,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 4.â€” An interesting</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+00D7 MULTIPLICATION SIGN :: 16 × 20, 3 large drawers: the</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L9: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -701,7 +705,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L9: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -711,7 +715,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L283: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • pear in the Saturday issue)</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -755,34 +763,38 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ONLY, NLY, DRESSERSâ€”Surface</t>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+00D7 MULTIPLICATION SIGN :: mirror 16×18, 4 large drawers</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L28: isolated marker/symbol line :: 1</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L299: punctuation artifact: repeated periods :: TELEPHONE CO.. LTD</t>
+          <t>L282: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: ♦ changes of advertisements ap- •</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • 4.30 o'clock on Friday after-•</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -798,12 +810,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -822,34 +834,38 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ONLY, CHIFFONIER â€” Ma-</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 4.â€”An interesting</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L31: isolated marker/symbol line :: 4</t>
+          <t>L28: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L418: punctuation artifact: repeated periods :: That experiment....</t>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • 4.30 o'clock on Friday after-•</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L715: line starts with punctuation glued to text :: * SILK and CREPE KIMONAS. SEPARATE SKIRTS-In White</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -879,7 +895,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>L552: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): WAISTSIn (odd internal casing) :: LADIESâ€™WAISTSIn all the various kinds wanted by those who</t>
+          <t>L552: suspicious token(s): LADIES’WAISTSIn (odd internal casing) :: LADIES’WAISTSIn all the various kinds wanted by those who</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
@@ -887,21 +903,17 @@
           <t>L564: suspicious token(s): 30I (letter/digit mix) :: Evg's 7.30I</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L201: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Quebec, Aug. 4.â€” Seven people,</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: letâ€� regiment.</t>
+          <t>L257: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ Until further notice The •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: 3</t>
+          <t>L31: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -912,7 +924,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L580: punctuation artifact: repeated periods :: ......New Majestic</t>
+          <t>L299: punctuation artifact: repeated periods :: TELEPHONE CO.. LTD</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -950,21 +962,17 @@
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L205: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Efforts io Settle VexedQ Question â€” Whole Trouble</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 ONLY, CHIFFONIER â€” Ma-</t>
+          <t>L259: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Gleaner will be published on •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 6</t>
+          <t>L32: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -975,7 +983,7 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L582: punctuation artifact: repeated periods :: .. Keystone Comedy</t>
+          <t>L418: punctuation artifact: repeated periods :: That experiment....</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -1013,21 +1021,17 @@
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L237: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 5 â€” The Daily across the ocean would be doubly so.</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 ONLY, PARLOR SUITEâ€”</t>
+          <t>L260: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: res. • Saturdays at noon.•</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 2</t>
+          <t>L34: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1038,7 +1042,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L584: punctuation artifact: repeated periods :: ............3 Reels</t>
+          <t>L580: punctuation artifact: repeated periods :: ......New Majestic</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1072,21 +1076,17 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: has paid attention â€”" has a lot to learn</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 ONLY DINNER SETâ€”A very</t>
+          <t>L262: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ Advertisers in order to have •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: â†’</t>
+          <t>L44: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1097,7 +1097,7 @@
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L586: punctuation artifact: repeated periods :: DEAD MAN'S SHOES ...........</t>
+          <t>L582: punctuation artifact: repeated periods :: .. Keystone Comedy</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1131,21 +1131,17 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L402: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: posal-discouraged it â€” sneered at it.</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L214: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: what the neighbors say," she doesnâ€™t</t>
+          <t>L279: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CHATEAU €</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L58: symbol-only separator/garbage line :: 1914.</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1156,7 +1152,7 @@
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>L588: punctuation artifact: repeated periods :: HIS SACRIFICE ..............</t>
+          <t>L584: punctuation artifact: repeated periods :: ............3 Reels</t>
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
@@ -1181,7 +1177,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1190,21 +1186,17 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L455: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WEDNESDAY â€” THE</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L257: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ Until further notice The â€¢</t>
+          <t>L282: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: ♦ changes of advertisements ap- •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 4</t>
+          <t>L58: symbol-only separator/garbage line :: 1914.</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1215,7 +1207,7 @@
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L590: punctuation artifact: repeated periods :: SIDETRACKED BY SISTER ......</t>
+          <t>L586: punctuation artifact: repeated periods :: DEAD MAN'S SHOES ...........</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1235,12 +1227,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1249,21 +1241,17 @@
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L485: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LADIES COATS â€” Very Stylish, in Silk, Lace, Poplin,</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L259: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Gleaner will be published on â€¢</t>
+          <t>L283: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • pear in the Saturday issue)</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: X</t>
+          <t>L62: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1274,7 +1262,7 @@
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>L592: punctuation artifact: repeated periods :: TOPLITSKY &amp; CO..............</t>
+          <t>L588: punctuation artifact: repeated periods :: HIS SACRIFICE ..............</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
@@ -1299,7 +1287,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1308,21 +1296,17 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PRETTY DRESSES â€” In Silk, White and Colored Serge, Linen</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L260: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: res. â€¢ Saturdays at noon.â€¢</t>
+          <t>L284: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ should have their copy at The •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 1</t>
+          <t>L63: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1331,7 +1315,11 @@
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
-      <c r="Q13" s="1" t="inlineStr"/>
+      <c r="Q13" s="1" t="inlineStr">
+        <is>
+          <t>L590: punctuation artifact: repeated periods :: SIDETRACKED BY SISTER ......</t>
+        </is>
+      </c>
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr"/>
       <c r="T13" s="1" t="inlineStr"/>
@@ -1354,7 +1342,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1363,21 +1351,17 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L552: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): WAISTSIn (odd internal casing) :: LADIESâ€™WAISTSIn all the various kinds wanted by those who</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ Advertisers in order to have â€¢</t>
+          <t>L285: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ Gleaner office not later than •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 1</t>
+          <t>L65: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1386,7 +1370,11 @@
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
-      <c r="Q14" s="1" t="inlineStr"/>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>L592: punctuation artifact: repeated periods :: TOPLITSKY &amp; CO..............</t>
+        </is>
+      </c>
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="1" t="inlineStr"/>
       <c r="T14" s="1" t="inlineStr"/>
@@ -1421,14 +1409,14 @@
       <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L272: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 32â€”Monahan, Mrs. T. V.,</t>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • 4.30 o'clock on Friday after-•</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 97</t>
+          <t>L70: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1472,14 +1460,14 @@
       <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L275: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 126-21â€”Kitchen, Mrs. S., res.</t>
+          <t>L287: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: &amp; noon •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 4</t>
+          <t>L77: isolated marker/symbol line :: 97</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1523,14 +1511,14 @@
       <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L279: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: CHATEAU â‚¬</t>
+          <t>L736: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: A</t>
+          <t>L82: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1560,21 +1548,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L280: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: A BRANDâ€”</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 0</t>
+          <t>L97: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L734: isolated marker/symbol line :: 1</t>
+          <t>L663: symbol-only separator/garbage line :: 7.30—10.30</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1599,21 +1583,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L282: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ changes of advertisements ap- â€¢</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L183: isolated marker/symbol line :: 317</t>
+          <t>L124: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L734: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1638,21 +1618,17 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L283: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ pear in the Saturday issue)</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L229: isolated marker/symbol line :: 4</t>
+          <t>L183: isolated marker/symbol line :: 317</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L757: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L736: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1677,21 +1653,17 @@
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L284: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ should have their copy at The â€¢</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L298: isolated marker/symbol line :: a</t>
+          <t>L229: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L761: isolated marker/symbol line :: (A</t>
+          <t>L757: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1716,19 +1688,19 @@
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L285: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ Gleaner office not later than â€¢</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L388: isolated marker/symbol line :: 20</t>
-        </is>
-      </c>
-      <c r="O22" s="1" t="inlineStr"/>
+          <t>L298: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>L761: isolated marker/symbol line :: (A</t>
+        </is>
+      </c>
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr"/>
       <c r="R22" s="1" t="inlineStr"/>
@@ -1751,16 +1723,12 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L286: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 4.30 o'clock on Friday after-â€¢</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L431: isolated marker/symbol line :: -</t>
+          <t>L388: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr"/>
@@ -1786,16 +1754,12 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L287: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: &amp; noon â€¢</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L449: isolated marker/symbol line :: &amp;</t>
+          <t>L431: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr"/>
@@ -1821,16 +1785,12 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L304: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Efforts to Settle Vexed Questionâ€” Whole Trouble</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L480: symbol-only separator/garbage line :: 7.30-10.30</t>
+          <t>L449: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr"/>
@@ -1856,16 +1816,12 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Quebec, Aug. 4.â€”Seven people,</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L514: isolated marker/symbol line :: a</t>
+          <t>L480: symbol-only separator/garbage line :: 7.30-10.30</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -1891,14 +1847,14 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 5â€”The Daily Tele-</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
-      <c r="N27" s="1" t="inlineStr"/>
+      <c r="N27" s="1" t="inlineStr">
+        <is>
+          <t>L514: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="O27" s="1" t="inlineStr"/>
       <c r="P27" s="1" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr"/>
@@ -1911,316 +1867,6 @@
       <c r="X27" s="1" t="inlineStr"/>
       <c r="Y27" s="1" t="inlineStr"/>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr"/>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr"/>
-      <c r="D28" s="1" t="inlineStr"/>
-      <c r="E28" s="1" t="inlineStr"/>
-      <c r="F28" s="1" t="inlineStr"/>
-      <c r="G28" s="1" t="inlineStr"/>
-      <c r="H28" s="1" t="inlineStr"/>
-      <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L419: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: has paid attentionâ€” has a lot to learn</t>
-        </is>
-      </c>
-      <c r="L28" s="1" t="inlineStr"/>
-      <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr"/>
-      <c r="O28" s="1" t="inlineStr"/>
-      <c r="P28" s="1" t="inlineStr"/>
-      <c r="Q28" s="1" t="inlineStr"/>
-      <c r="R28" s="1" t="inlineStr"/>
-      <c r="S28" s="1" t="inlineStr"/>
-      <c r="T28" s="1" t="inlineStr"/>
-      <c r="U28" s="1" t="inlineStr"/>
-      <c r="V28" s="1" t="inlineStr"/>
-      <c r="W28" s="1" t="inlineStr"/>
-      <c r="X28" s="1" t="inlineStr"/>
-      <c r="Y28" s="1" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr"/>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr"/>
-      <c r="D29" s="1" t="inlineStr"/>
-      <c r="E29" s="1" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr"/>
-      <c r="G29" s="1" t="inlineStr"/>
-      <c r="H29" s="1" t="inlineStr"/>
-      <c r="I29" s="1" t="inlineStr"/>
-      <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L453: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: posalâ€”discouraged itâ€”sneered at it.</t>
-        </is>
-      </c>
-      <c r="L29" s="1" t="inlineStr"/>
-      <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="inlineStr"/>
-      <c r="O29" s="1" t="inlineStr"/>
-      <c r="P29" s="1" t="inlineStr"/>
-      <c r="Q29" s="1" t="inlineStr"/>
-      <c r="R29" s="1" t="inlineStr"/>
-      <c r="S29" s="1" t="inlineStr"/>
-      <c r="T29" s="1" t="inlineStr"/>
-      <c r="U29" s="1" t="inlineStr"/>
-      <c r="V29" s="1" t="inlineStr"/>
-      <c r="W29" s="1" t="inlineStr"/>
-      <c r="X29" s="1" t="inlineStr"/>
-      <c r="Y29" s="1" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr"/>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr"/>
-      <c r="D30" s="1" t="inlineStr"/>
-      <c r="E30" s="1" t="inlineStr"/>
-      <c r="F30" s="1" t="inlineStr"/>
-      <c r="G30" s="1" t="inlineStr"/>
-      <c r="H30" s="1" t="inlineStr"/>
-      <c r="I30" s="1" t="inlineStr"/>
-      <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L463: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Sir Wilfrid Laurierâ€™s Government</t>
-        </is>
-      </c>
-      <c r="L30" s="1" t="inlineStr"/>
-      <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="inlineStr"/>
-      <c r="O30" s="1" t="inlineStr"/>
-      <c r="P30" s="1" t="inlineStr"/>
-      <c r="Q30" s="1" t="inlineStr"/>
-      <c r="R30" s="1" t="inlineStr"/>
-      <c r="S30" s="1" t="inlineStr"/>
-      <c r="T30" s="1" t="inlineStr"/>
-      <c r="U30" s="1" t="inlineStr"/>
-      <c r="V30" s="1" t="inlineStr"/>
-      <c r="W30" s="1" t="inlineStr"/>
-      <c r="X30" s="1" t="inlineStr"/>
-      <c r="Y30" s="1" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr"/>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr"/>
-      <c r="D31" s="1" t="inlineStr"/>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr"/>
-      <c r="G31" s="1" t="inlineStr"/>
-      <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Rev. Dr, W. H. Smithâ€™s Views</t>
-        </is>
-      </c>
-      <c r="L31" s="1" t="inlineStr"/>
-      <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
-      <c r="O31" s="1" t="inlineStr"/>
-      <c r="P31" s="1" t="inlineStr"/>
-      <c r="Q31" s="1" t="inlineStr"/>
-      <c r="R31" s="1" t="inlineStr"/>
-      <c r="S31" s="1" t="inlineStr"/>
-      <c r="T31" s="1" t="inlineStr"/>
-      <c r="U31" s="1" t="inlineStr"/>
-      <c r="V31" s="1" t="inlineStr"/>
-      <c r="W31" s="1" t="inlineStr"/>
-      <c r="X31" s="1" t="inlineStr"/>
-      <c r="Y31" s="1" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr"/>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr"/>
-      <c r="D32" s="1" t="inlineStr"/>
-      <c r="E32" s="1" t="inlineStr"/>
-      <c r="F32" s="1" t="inlineStr"/>
-      <c r="G32" s="1" t="inlineStr"/>
-      <c r="H32" s="1" t="inlineStr"/>
-      <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L558: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: -_ /â€˜yers for those whom</t>
-        </is>
-      </c>
-      <c r="L32" s="1" t="inlineStr"/>
-      <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr"/>
-      <c r="O32" s="1" t="inlineStr"/>
-      <c r="P32" s="1" t="inlineStr"/>
-      <c r="Q32" s="1" t="inlineStr"/>
-      <c r="R32" s="1" t="inlineStr"/>
-      <c r="S32" s="1" t="inlineStr"/>
-      <c r="T32" s="1" t="inlineStr"/>
-      <c r="U32" s="1" t="inlineStr"/>
-      <c r="V32" s="1" t="inlineStr"/>
-      <c r="W32" s="1" t="inlineStr"/>
-      <c r="X32" s="1" t="inlineStr"/>
-      <c r="Y32" s="1" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr"/>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr"/>
-      <c r="D33" s="1" t="inlineStr"/>
-      <c r="E33" s="1" t="inlineStr"/>
-      <c r="F33" s="1" t="inlineStr"/>
-      <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" s="1" t="inlineStr"/>
-      <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L654: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LADIES' LONG COATSâ€” Very Stylish, in Silk, Lace, Poplin,</t>
-        </is>
-      </c>
-      <c r="L33" s="1" t="inlineStr"/>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr"/>
-      <c r="P33" s="1" t="inlineStr"/>
-      <c r="Q33" s="1" t="inlineStr"/>
-      <c r="R33" s="1" t="inlineStr"/>
-      <c r="S33" s="1" t="inlineStr"/>
-      <c r="T33" s="1" t="inlineStr"/>
-      <c r="U33" s="1" t="inlineStr"/>
-      <c r="V33" s="1" t="inlineStr"/>
-      <c r="W33" s="1" t="inlineStr"/>
-      <c r="X33" s="1" t="inlineStr"/>
-      <c r="Y33" s="1" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr"/>
-      <c r="B34" s="1" t="inlineStr"/>
-      <c r="C34" s="1" t="inlineStr"/>
-      <c r="D34" s="1" t="inlineStr"/>
-      <c r="E34" s="1" t="inlineStr"/>
-      <c r="F34" s="1" t="inlineStr"/>
-      <c r="G34" s="1" t="inlineStr"/>
-      <c r="H34" s="1" t="inlineStr"/>
-      <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L663: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 7.30â€”10.30</t>
-        </is>
-      </c>
-      <c r="L34" s="1" t="inlineStr"/>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr"/>
-      <c r="P34" s="1" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr"/>
-      <c r="R34" s="1" t="inlineStr"/>
-      <c r="S34" s="1" t="inlineStr"/>
-      <c r="T34" s="1" t="inlineStr"/>
-      <c r="U34" s="1" t="inlineStr"/>
-      <c r="V34" s="1" t="inlineStr"/>
-      <c r="W34" s="1" t="inlineStr"/>
-      <c r="X34" s="1" t="inlineStr"/>
-      <c r="Y34" s="1" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr"/>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr"/>
-      <c r="D35" s="1" t="inlineStr"/>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr"/>
-      <c r="G35" s="1" t="inlineStr"/>
-      <c r="H35" s="1" t="inlineStr"/>
-      <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L676: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PRETTY DRESSES â€” In Silk, White and Colored Serge, Linen</t>
-        </is>
-      </c>
-      <c r="L35" s="1" t="inlineStr"/>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr"/>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr"/>
-      <c r="R35" s="1" t="inlineStr"/>
-      <c r="S35" s="1" t="inlineStr"/>
-      <c r="T35" s="1" t="inlineStr"/>
-      <c r="U35" s="1" t="inlineStr"/>
-      <c r="V35" s="1" t="inlineStr"/>
-      <c r="W35" s="1" t="inlineStr"/>
-      <c r="X35" s="1" t="inlineStr"/>
-      <c r="Y35" s="1" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr"/>
-      <c r="B36" s="1" t="inlineStr"/>
-      <c r="C36" s="1" t="inlineStr"/>
-      <c r="D36" s="1" t="inlineStr"/>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr"/>
-      <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L36" s="1" t="inlineStr"/>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr"/>
-      <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr"/>
-      <c r="R36" s="1" t="inlineStr"/>
-      <c r="S36" s="1" t="inlineStr"/>
-      <c r="T36" s="1" t="inlineStr"/>
-      <c r="U36" s="1" t="inlineStr"/>
-      <c r="V36" s="1" t="inlineStr"/>
-      <c r="W36" s="1" t="inlineStr"/>
-      <c r="X36" s="1" t="inlineStr"/>
-      <c r="Y36" s="1" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr"/>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr"/>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L757: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
-      <c r="R37" s="1" t="inlineStr"/>
-      <c r="S37" s="1" t="inlineStr"/>
-      <c r="T37" s="1" t="inlineStr"/>
-      <c r="U37" s="1" t="inlineStr"/>
-      <c r="V37" s="1" t="inlineStr"/>
-      <c r="W37" s="1" t="inlineStr"/>
-      <c r="X37" s="1" t="inlineStr"/>
-      <c r="Y37" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
